--- a/docs/aluminium_parts_3dprint_masses.xlsx
+++ b/docs/aluminium_parts_3dprint_masses.xlsx
@@ -2867,12 +2867,18 @@
       <c r="D15" s="8" t="n">
         <v>616.53</v>
       </c>
-      <c r="E15" s="9" t="n"/>
+      <c r="E15" s="12" t="n">
+        <v>119</v>
+      </c>
       <c r="F15" s="10">
         <f>IF(E15="","",E15/D15)</f>
         <v/>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>사진6,7,10 '119 (114? 124?)' · 불확실 · 발판. 세 사진 모두 11x로 읽히나 마지막 자리 불명. 비율 0.19 - 두꺼운 판이라 저충전 출력 가능성</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="92" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -3074,7 +3080,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>사진4 '84.5' · 불확실 · 대안: HipRoll2Yaw_Mount (165 g) · 세로로 선 판. 84.5 g를 PLA 상한 안에서 낼 수 있는 힙 부품은 CAD 199 g인 이 부품뿐(비율 0.42)</t>
+          <t>사진4,9 '84.5 / '8ㅂ'' · 불확실 · 대안: HipRoll2Yaw_Mount면 0.51로 물리 불가 · 사진9에서는 X-래티스 블록 위에 적힌 것으로 보여 배정이 틀렸을 수 있음. 그러나 84.5 g를 PLA 상한(0.46) 안에서 낼 수 있는 힙 부품은 CAD 199 g인 이 부품뿐</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3099,18 @@
       <c r="D25" s="8" t="n">
         <v>147.98</v>
       </c>
-      <c r="E25" s="9" t="n"/>
+      <c r="E25" s="12" t="n">
+        <v>53</v>
+      </c>
       <c r="F25" s="10">
         <f>IF(E25="","",E25/D25)</f>
         <v/>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>사진6 '53.0 (23.0?)' · 불확실 · 대안: HipPitch2Roll_A (128 g, 0.41) · 사진6 좌상단 힙 피치 D판. 비율 0.36</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="92" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -3188,7 +3200,7 @@
         <v>164.61</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>67</v>
+        <v>67.3</v>
       </c>
       <c r="F29" s="10">
         <f>IF(E29="","",E29/D29)</f>
@@ -3196,7 +3208,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>사진3,4 '67' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · RS04가 들어앉은 X-래티스 블록, 대형 베어링 위</t>
+          <t>사진3,4,8 '67 / 67.3' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · 요 모터 둘레 칼라(사진8 '67.3')가 사진3의 '67'과 같은 부품 - 소수점 보정</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3249,18 @@
       <c r="D31" s="8" t="n">
         <v>39.27</v>
       </c>
-      <c r="E31" s="9" t="n"/>
+      <c r="E31" s="9" t="n">
+        <v>13.4</v>
+      </c>
       <c r="F31" s="10">
         <f>IF(E31="","",E31/D31)</f>
         <v/>
       </c>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>사진10 '13.4' · 보통 · 힙 요 모터 위 소형 X-래티스 블록(사진10 맨 위). 비율 0.34</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="92" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -3347,12 +3365,18 @@
       <c r="D36" s="8" t="n">
         <v>168.52</v>
       </c>
-      <c r="E36" s="9" t="n"/>
+      <c r="E36" s="12" t="n">
+        <v>36.9</v>
+      </c>
       <c r="F36" s="10">
         <f>IF(E36="","",E36/D36)</f>
         <v/>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>사진7 '36.9 (56.9?)' · 불확실 · 대안: KneeB2AnkleB (172 g) · 무릎→발목 긴 트러스판. 36.9면 비율 0.22로 다른 부품보다 낮음(충전율 차이 가능) - 56.9면 0.34. 3/5 판독 재확인</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="92" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -3691,12 +3715,18 @@
       <c r="D50" s="8" t="n">
         <v>32.19</v>
       </c>
-      <c r="E50" s="9" t="n"/>
+      <c r="E50" s="9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="F50" s="10">
         <f>IF(E50="","",E50/D50)</f>
         <v/>
       </c>
-      <c r="G50" s="6" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>사진7,8 '10.9' · 보통 · 대안: AnkleA2B_A_L (35 g, 0.31) - 같은 계열 4종(32~39 g) 중 어느 것인지는 미확정 · RS03 위쪽 마운트판, 두 사진에서 같은 값. 비율 0.34</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="92" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
@@ -3713,12 +3743,18 @@
       <c r="D51" s="8" t="n">
         <v>32.19</v>
       </c>
-      <c r="E51" s="9" t="n"/>
+      <c r="E51" s="12" t="n">
+        <v>10.8</v>
+      </c>
       <c r="F51" s="10">
         <f>IF(E51="","",E51/D51)</f>
         <v/>
       </c>
-      <c r="G51" s="6" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>사진7 '10.8' · 불확실 · 대안: 같은 계열 4종 중 하나 · RS03 아래쪽 마운트판. 비율 0.34</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="92" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -3792,7 +3828,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>사진1 '6.0' · 불확실 · 발목 우측 소형 부품. 비율 0.29</t>
+          <t>사진1,10 '6.0 (사진10은 6.9?)' · 불확실 · 발목 소형 부품. 비율 0.29~0.34</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3922,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>사진1 '98.1' · 보통 · 무릎 로터쪽 허벅지 트러스판. A/B 한 쌍 중 어느 쪽인지는 사진만으로 확정 불가 - 반대편 판에 적힌 값과 대조</t>
+          <t>사진1,8 '98.1 (사진8은 98.4로도 읽힘)' · 보통 · 대안: Yaw2KneePlateB - 반대편 판 값 미확인 · 무릎 로터쪽 허벅지 트러스판. 두 사진 모두 이 판 - 같은 값의 판독 차이</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3985,18 @@
       <c r="D61" s="8" t="n">
         <v>139.88</v>
       </c>
-      <c r="E61" s="9" t="n"/>
+      <c r="E61" s="9" t="n">
+        <v>44.9</v>
+      </c>
       <c r="F61" s="10">
         <f>IF(E61="","",E61/D61)</f>
         <v/>
       </c>
-      <c r="G61" s="6" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>사진10 '44.9' · 보통 · 요 모터 바로 아래 흰 링. 비율 0.32</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="92" customHeight="1">
       <c r="A62" s="6" t="inlineStr">

--- a/docs/aluminium_parts_3dprint_masses.xlsx
+++ b/docs/aluminium_parts_3dprint_masses.xlsx
@@ -79,7 +79,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8F0C8"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +164,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2868,7 +2876,7 @@
         <v>616.53</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>119</v>
+        <v>181.9</v>
       </c>
       <c r="F15" s="10">
         <f>IF(E15="","",E15/D15)</f>
@@ -2876,7 +2884,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>사진6,7,10 '119 (114? 124?)' · 불확실 · 발판. 세 사진 모두 11x로 읽히나 마지막 자리 불명. 비율 0.19 - 두꺼운 판이라 저충전 출력 가능성</t>
+          <t>사진user '181.9 (사용자 확인)' · 확실 · 발판. 사진 판독 119는 오독 - 사용자가 저울값 181.9로 확정. 비율 0.295</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3079,7 @@
       <c r="D24" s="8" t="n">
         <v>199.2</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="13" t="n">
         <v>84.5</v>
       </c>
       <c r="F24" s="10">
@@ -3099,7 +3107,7 @@
       <c r="D25" s="8" t="n">
         <v>147.98</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>53</v>
       </c>
       <c r="F25" s="10">
@@ -3200,7 +3208,7 @@
         <v>164.61</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="F29" s="10">
         <f>IF(E29="","",E29/D29)</f>
@@ -3208,7 +3216,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>사진3,4,8 '67 / 67.3' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · 요 모터 둘레 칼라(사진8 '67.3')가 사진3의 '67'과 같은 부품 - 소수점 보정</t>
+          <t>사진3,4 '67' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · RS04가 들어앉은 X-래티스 블록. 사진8의 '6x.3'을 이 부품으로 봤던 것은 철회(그건 HipYaw2Knee 63.3)</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3374,7 @@
         <v>168.52</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>36.9</v>
+        <v>56.9</v>
       </c>
       <c r="F36" s="10">
         <f>IF(E36="","",E36/D36)</f>
@@ -3374,7 +3382,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>사진7 '36.9 (56.9?)' · 불확실 · 대안: KneeB2AnkleB (172 g) · 무릎→발목 긴 트러스판. 36.9면 비율 0.22로 다른 부품보다 낮음(충전율 차이 가능) - 56.9면 0.34. 3/5 판독 재확인</t>
+          <t>사진user '56.9 (사용자 확인)' · 확실 · 정강이 긴 트러스(motorb2ankle). 사진의 '36.9'는 3/5 오독 - 56.9 확정. A/B 짝 중 어느 쪽인지는 미확정</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3479,7 @@
       <c r="D40" s="8" t="n">
         <v>123.63</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>41.1</v>
       </c>
       <c r="F40" s="10">
@@ -3637,7 +3645,7 @@
       <c r="D47" s="8" t="n">
         <v>39.37</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="13" t="n">
         <v>12</v>
       </c>
       <c r="F47" s="10">
@@ -3687,7 +3695,7 @@
       <c r="D49" s="8" t="n">
         <v>35.22</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="13" t="n">
         <v>11.3</v>
       </c>
       <c r="F49" s="10">
@@ -3743,7 +3751,7 @@
       <c r="D51" s="8" t="n">
         <v>32.19</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>10.8</v>
       </c>
       <c r="F51" s="10">
@@ -3819,7 +3827,7 @@
       <c r="D54" s="8" t="n">
         <v>20.54</v>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="13" t="n">
         <v>6</v>
       </c>
       <c r="F54" s="10">
@@ -3941,12 +3949,18 @@
       <c r="D59" s="8" t="n">
         <v>317.19</v>
       </c>
-      <c r="E59" s="9" t="n"/>
+      <c r="E59" s="9" t="n">
+        <v>63.3</v>
+      </c>
       <c r="F59" s="10">
         <f>IF(E59="","",E59/D59)</f>
         <v/>
       </c>
-      <c r="G59" s="6" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>사진user,8 '63.3 (사용자: hipyaw2knee)' · 보통 · 대안: HipYaw2Knee_outer (140 g)면 0.45로 상한 직전 - 사용자 명칭 hipyaw2knee가 어느 바디인지 확인 · 요 로터에 붙는 두꺼운 원판(317 g). 사진8의 '6x.3'은 이 부품이었음. 비율 0.20 - 두꺼운 부품 저충전</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="92" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -4013,7 +4027,7 @@
       <c r="D62" s="8" t="n">
         <v>106.36</v>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="E62" s="13" t="n">
         <v>40</v>
       </c>
       <c r="F62" s="10">
@@ -4041,10 +4055,10 @@
       <c r="D63" s="8" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="E63" s="13" t="n">
         <v>40.5</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="14">
         <f>IF(E63="","",E63/D63)</f>
         <v/>
       </c>
@@ -4621,16 +4635,16 @@
       <c r="G86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="C87" s="14" t="inlineStr">
+      <c r="C87" s="15" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="D87" s="15">
+      <c r="D87" s="16">
         <f>SUM(D6:D86)</f>
         <v/>
       </c>
-      <c r="E87" s="15">
+      <c r="E87" s="16">
         <f>SUM(E6:E86)</f>
         <v/>
       </c>
@@ -4659,7 +4673,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>링크별 합계 — E열에 측정값을 넣는 대로 자동으로 채워집니다</t>
         </is>
@@ -4702,15 +4716,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A4)</f>
         <v/>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4725,15 +4739,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A5)</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4748,15 +4762,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A6)</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4771,15 +4785,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A7)</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4794,15 +4808,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A8)</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4817,15 +4831,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A9)</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4840,15 +4854,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A10)</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4863,15 +4877,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A11)</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4886,15 +4900,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A12)</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4909,15 +4923,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A13)</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4932,15 +4946,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A14)</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4955,38 +4969,38 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A15)</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="18">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <f>SUM(B4:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>SUM(C4:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>SUM(D4:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>SUM(E4:E15)</f>
         <v/>
       </c>

--- a/docs/aluminium_parts_3dprint_masses.xlsx
+++ b/docs/aluminium_parts_3dprint_masses.xlsx
@@ -79,7 +79,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +111,11 @@
         <fgColor rgb="00FFD4A8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9DEE5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +172,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2609,7 +2617,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>E열 기입값은 출력물 사진의 손글씨를 읽어 CAD 부품에 대조한 것 — 초록=확실 · 노랑=보통(A/B 짝 미확정) · 주황=불확실(실물 대조 필요). F열이 46 %를 넘으면 빨강: PLA(1.24)/알루(2.70) 물리 상한 초과 = 오독 또는 오배정.</t>
+          <t>E열 기입값은 출력물 사진의 손글씨를 읽어 CAD 부품에 대조한 것 — 초록=확실 · 노랑=보통(A/B 짝 미확정) · 주황=불확실(실물 대조 필요) · 회색=알루미늄 가공품(CAD 질량 그대로). F열이 46 %를 넘으면 빨강: PLA(1.24)/알루(2.70) 물리 상한 초과 = 오독 또는 오배정.</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3293,18 @@
       <c r="D32" s="8" t="n">
         <v>54.76</v>
       </c>
-      <c r="E32" s="9" t="n"/>
+      <c r="E32" s="14" t="n">
+        <v>54.76</v>
+      </c>
       <c r="F32" s="10">
         <f>IF(E32="","",E32/D32)</f>
         <v/>
       </c>
-      <c r="G32" s="6" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="92" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -3673,12 +3687,18 @@
       <c r="D48" s="8" t="n">
         <v>38.77</v>
       </c>
-      <c r="E48" s="9" t="n"/>
+      <c r="E48" s="14" t="n">
+        <v>38.77</v>
+      </c>
       <c r="F48" s="10">
         <f>IF(E48="","",E48/D48)</f>
         <v/>
       </c>
-      <c r="G48" s="6" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="92" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -4058,7 +4078,7 @@
       <c r="E63" s="13" t="n">
         <v>40.5</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="15">
         <f>IF(E63="","",E63/D63)</f>
         <v/>
       </c>
@@ -4635,16 +4655,16 @@
       <c r="G86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="C87" s="15" t="inlineStr">
+      <c r="C87" s="16" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="D87" s="16">
+      <c r="D87" s="17">
         <f>SUM(D6:D86)</f>
         <v/>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="17">
         <f>SUM(E6:E86)</f>
         <v/>
       </c>
@@ -4673,7 +4693,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>링크별 합계 — E열에 측정값을 넣는 대로 자동으로 채워집니다</t>
         </is>
@@ -4716,15 +4736,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A4)</f>
         <v/>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4739,15 +4759,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A5)</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4762,15 +4782,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A6)</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4785,15 +4805,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A7)</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4808,15 +4828,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A8)</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4831,15 +4851,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A9)</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4854,15 +4874,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A10)</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4877,15 +4897,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A11)</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4900,15 +4920,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A12)</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4923,15 +4943,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A13)</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4946,15 +4966,15 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A14)</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -4969,38 +4989,38 @@
         <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A15)</f>
         <v/>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$D$6:$D$86)</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>SUM(B4:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <f>SUM(C4:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>SUM(D4:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>SUM(E4:E15)</f>
         <v/>
       </c>

--- a/docs/aluminium_parts_3dprint_masses.xlsx
+++ b/docs/aluminium_parts_3dprint_masses.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="링크별 집계" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'알루미늄 부품'!$A$5:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'알루미늄 부품'!$A$5:$G$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F7"/>
+        <fgColor rgb="00C8F0C8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8F0C8"/>
+        <fgColor rgb="00F2F4F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,11 +165,11 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1529,756 +1529,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>57</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>58</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>64</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>74</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>77</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>84</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1485900" cy="1114425"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2581,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2610,7 +1860,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>출처: Fusion 360 문서 260819_HumanMesh_wUpper_OMAKASE v4, 살아있는(표시된) 바디 81개 · 사진은 각 바디의 메시를 단독 렌더한 것</t>
+          <t>출처: Fusion 360 문서 260814_HumanMesh_OMAKASE_RrecoverFromCrash v5 (2026-08-15 19:07 UTC (= 2026-08-16 04:07 KST)), 알루미늄 바디 51개 (숨은 바디 1개 포함) · 사진은 각 바디의 메시를 단독 렌더한 것</t>
         </is>
       </c>
     </row>
@@ -2667,22 +1917,18 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>NoSim_2-RSU-Originator / Body1</t>
+          <t>6810ZZ</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>54.69</v>
+        <v>16.52</v>
       </c>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10">
         <f>IF(E6="","",E6/D6)</f>
         <v/>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>설계 참조용 (NoSim) — 실물 아님</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -2693,22 +1939,18 @@
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>NoSim_2-RSU-Originator / Body2</t>
+          <t>6810ZZ (1) / 6810ZZ</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>42.59</v>
+        <v>16.52</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10">
         <f>IF(E7="","",E7/D7)</f>
         <v/>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>설계 참조용 (NoSim) — 실물 아님</t>
-        </is>
-      </c>
+      <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -2735,28 +1977,24 @@
     <row r="9" ht="92" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>arm_link (팔)</t>
+          <t>base_link (골반)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>DR2020-375L-ArmR / DR2020-375L (1)</t>
+          <t>CenterParts / BaseLink_Bottom_A</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>293.43</v>
+        <v>195.79</v>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10">
         <f>IF(E9="","",E9/D9)</f>
         <v/>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="92" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -2767,11 +2005,11 @@
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>CenterParts / BaseLink_Bottom_A</t>
+          <t>CenterParts / BaseLink_Bottom_B</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>195.79</v>
+        <v>195.28</v>
       </c>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10">
@@ -2789,11 +2027,11 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>CenterParts / BaseLink_Bottom_B</t>
+          <t>CenterParts / Baselink_toWaistYaw</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>195.28</v>
+        <v>192.39</v>
       </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10">
@@ -2811,11 +2049,11 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>CenterParts / Baselink_toWaistYaw</t>
+          <t>CenterParts / Baselink_Connect_Fr</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>192.39</v>
+        <v>100.22</v>
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10">
@@ -2833,7 +2071,7 @@
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>CenterParts / Baselink_Connect_Fr</t>
+          <t>CenterParts / Baselink_Connect_Ba</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
@@ -2849,24 +2087,30 @@
     <row r="14" ht="92" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>base_link (골반)</t>
+          <t>foot_link (발)</t>
         </is>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>CenterParts / Baselink_Connect_Ba</t>
+          <t>Ankle2Feet / FEET</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>100.22</v>
-      </c>
-      <c r="E14" s="9" t="n"/>
+        <v>617.72</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>181.9</v>
+      </c>
       <c r="F14" s="10">
         <f>IF(E14="","",E14/D14)</f>
         <v/>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>사진user '181.9 (사용자 확인)' · 확실 · 발판. 사진 판독 119는 오독 - 사용자가 저울값 181.9로 확정. 비율 0.295</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="92" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -2877,24 +2121,18 @@
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / FEET</t>
+          <t>Ankle2Feet / AnkleFeetPillowAB</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>616.53</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>181.9</v>
-      </c>
+        <v>104.59</v>
+      </c>
+      <c r="E15" s="9" t="n"/>
       <c r="F15" s="10">
         <f>IF(E15="","",E15/D15)</f>
         <v/>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>사진user '181.9 (사용자 확인)' · 확실 · 발판. 사진 판독 119는 오독 - 사용자가 저울값 181.9로 확정. 비율 0.295</t>
-        </is>
-      </c>
+      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="92" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -2905,11 +2143,11 @@
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / AnkleFeetPillowAB</t>
+          <t>Ankle2Feet / AnkleFeetPillowA</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>105.16</v>
+        <v>39.3</v>
       </c>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10">
@@ -2927,11 +2165,11 @@
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / AnkleFeetPillowA</t>
+          <t>Ankle2Feet / AnkleFeetPillowB</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>40.88</v>
+        <v>39.3</v>
       </c>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="10">
@@ -2943,61 +2181,73 @@
     <row r="18" ht="92" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_pitch_link</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / AnkleFeetPillowB</t>
+          <t>HipPitch2Roll / HipPitchRotor</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>40.88</v>
-      </c>
-      <c r="E18" s="9" t="n"/>
+        <v>232.45</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>84.5</v>
+      </c>
       <c r="F18" s="10">
         <f>IF(E18="","",E18/D18)</f>
         <v/>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>사진4,9 '84.5 / '8ㅂ'' · 불확실 · 대안: HipRoll2Yaw_Mount면 0.51로 물리 불가 · 사진9에서는 X-래티스 블록 위에 적힌 것으로 보여 배정이 틀렸을 수 있음. 그러나 84.5 g를 PLA 상한(0.46) 안에서 낼 수 있는 힙 부품은 CAD 199 g인 이 부품뿐</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="92" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_pitch_link</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Ankle_Stopper_Roll</t>
+          <t>HipPitch2Roll / HipPitch2Roll_B</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="E19" s="9" t="n"/>
+        <v>168.7</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>53</v>
+      </c>
       <c r="F19" s="10">
         <f>IF(E19="","",E19/D19)</f>
         <v/>
       </c>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>사진6 '53.0 (23.0?)' · 불확실 · 대안: HipPitch2Roll_A (128 g, 0.41) · 사진6 좌상단 힙 피치 D판. 비율 0.36</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="92" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_pitch_link</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Flange / 20deg_flangeA</t>
+          <t>HipPitch2Roll / HipPitch2Roll_A</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0.32</v>
+        <v>145.25</v>
       </c>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="10">
@@ -3009,17 +2259,17 @@
     <row r="21" ht="92" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_pitch_link</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Flange / 20deg_flangeB</t>
+          <t>HipPitch2Roll / HipPitchFlange</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0.32</v>
+        <v>107.5</v>
       </c>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10">
@@ -3031,295 +2281,301 @@
     <row r="22" ht="92" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_roll_link</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Flange(Mirror) / 20deg_flangeA</t>
+          <t>PipRoll2Yaw / HipRoll2YawA</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E22" s="9" t="n"/>
+        <v>194.83</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>57.2</v>
+      </c>
       <c r="F22" s="10">
         <f>IF(E22="","",E22/D22)</f>
         <v/>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>사진2,4 '57.2 (두 사진 모두)' · 보통 · 대안: HipRoll2YawB (136 g) · 요 모터 바로 위 둥근 판, 상단 6볼트 로터 패턴. 사진 2와 4에서 같은 값 확인</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="92" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_roll_link</t>
         </is>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Flange(Mirror) / 20deg_flangeB</t>
+          <t>PipRoll2Yaw / HipRoll2Yaw_Mount</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E23" s="9" t="n"/>
+        <v>164.61</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>67</v>
+      </c>
       <c r="F23" s="10">
         <f>IF(E23="","",E23/D23)</f>
         <v/>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>사진3,4 '67' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · RS04가 들어앉은 X-래티스 블록. 사진8의 '6x.3'을 이 부품으로 봤던 것은 철회(그건 HipYaw2Knee 63.3)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="92" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>hip_pitch_link</t>
+          <t>hip_roll_link</t>
         </is>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>HipPitch2Roll / HipPitchRotor</t>
+          <t>PipRoll2Yaw / HipRoll2YawB</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>84.5</v>
-      </c>
+        <v>164.46</v>
+      </c>
+      <c r="E24" s="9" t="n"/>
       <c r="F24" s="10">
         <f>IF(E24="","",E24/D24)</f>
         <v/>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>사진4,9 '84.5 / '8ㅂ'' · 불확실 · 대안: HipRoll2Yaw_Mount면 0.51로 물리 불가 · 사진9에서는 X-래티스 블록 위에 적힌 것으로 보여 배정이 틀렸을 수 있음. 그러나 84.5 g를 PLA 상한(0.46) 안에서 낼 수 있는 힙 부품은 CAD 199 g인 이 부품뿐</t>
-        </is>
-      </c>
+      <c r="G24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="92" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>hip_pitch_link</t>
+          <t>hip_roll_link</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>HipPitch2Roll / HipPitch2Roll_B</t>
+          <t>PipRoll2Yaw / Body4</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>147.98</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>53</v>
+        <v>39.27</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>13.4</v>
       </c>
       <c r="F25" s="10">
         <f>IF(E25="","",E25/D25)</f>
         <v/>
       </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>사진6 '53.0 (23.0?)' · 불확실 · 대안: HipPitch2Roll_A (128 g, 0.41) · 사진6 좌상단 힙 피치 D판. 비율 0.36</t>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>사진10 '13.4' · 보통 · 힙 요 모터 위 소형 X-래티스 블록(사진10 맨 위). 비율 0.34</t>
         </is>
       </c>
     </row>
     <row r="26" ht="92" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>hip_pitch_link</t>
+          <t>shin/foot (푸시로드)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>HipPitch2Roll / HipPitch2Roll_A</t>
+          <t>Ankle2Feet / Arm_A</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>128.16</v>
-      </c>
-      <c r="E26" s="9" t="n"/>
+        <v>54.76</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>54.76</v>
+      </c>
       <c r="F26" s="10">
         <f>IF(E26="","",E26/D26)</f>
         <v/>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="92" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>hip_pitch_link</t>
+          <t>shin/foot (푸시로드)</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>HipPitch2Roll / HipPitchFlange</t>
+          <t>Ankle2Feet / Arm_B</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>106.97</v>
-      </c>
-      <c r="E27" s="9" t="n"/>
+        <v>41.55</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>41.55</v>
+      </c>
       <c r="F27" s="10">
         <f>IF(E27="","",E27/D27)</f>
         <v/>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="92" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>hip_roll_link</t>
+          <t>shin/foot (푸시로드)</t>
         </is>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>HipRoll2Yaw / HipRoll2YawA</t>
+          <t>Ankle2Feet / AnkleBraceA</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>165.46</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>57.2</v>
-      </c>
+        <v>40.87</v>
+      </c>
+      <c r="E28" s="9" t="n"/>
       <c r="F28" s="10">
         <f>IF(E28="","",E28/D28)</f>
         <v/>
       </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>사진2,4 '57.2 (두 사진 모두)' · 보통 · 대안: HipRoll2YawB (136 g) · 요 모터 바로 위 둥근 판, 상단 6볼트 로터 패턴. 사진 2와 4에서 같은 값 확인</t>
-        </is>
-      </c>
+      <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="92" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>hip_roll_link</t>
+          <t>shin/foot (푸시로드)</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>HipRoll2Yaw / HipRoll2Yaw_Mount</t>
+          <t>Ankle2Feet / AnkleBraceB</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>164.61</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>67</v>
-      </c>
+        <v>40.87</v>
+      </c>
+      <c r="E29" s="9" t="n"/>
       <c r="F29" s="10">
         <f>IF(E29="","",E29/D29)</f>
         <v/>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>사진3,4 '67' · 보통 · 대안: HipPitch2Roll_B (148 g, 비율 0.45 - 상한 직전) · RS04가 들어앉은 X-래티스 블록. 사진8의 '6x.3'을 이 부품으로 봤던 것은 철회(그건 HipYaw2Knee 63.3)</t>
-        </is>
-      </c>
+      <c r="G29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="92" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>hip_roll_link</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>HipRoll2Yaw / HipRoll2YawB</t>
+          <t>Knee2Ankle / Knee2Ankle_RotorSide_1</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="E30" s="9" t="n"/>
+        <v>176.5</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>61.2</v>
+      </c>
       <c r="F30" s="10">
         <f>IF(E30="","",E30/D30)</f>
         <v/>
       </c>
-      <c r="G30" s="6" t="inlineStr"/>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>사진1 '61.2' · 보통 · D형 판, 중앙 베어링 둘레 8볼트(로터 체결)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="92" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>hip_roll_link</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>HipRoll2Yaw / Body4</t>
+          <t>Ankle2Feet / KneeB2AnkleA</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>13.4</v>
+        <v>167.54</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>56.9</v>
       </c>
       <c r="F31" s="10">
         <f>IF(E31="","",E31/D31)</f>
         <v/>
       </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>사진10 '13.4' · 보통 · 힙 요 모터 위 소형 X-래티스 블록(사진10 맨 위). 비율 0.34</t>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>사진user '56.9 (사용자 확인)' · 확실 · 정강이 긴 트러스(motorb2ankle). 사진의 '36.9'는 3/5 오독 - 56.9 확정. A/B 짝 중 어느 쪽인지는 미확정</t>
         </is>
       </c>
     </row>
     <row r="32" ht="92" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>shin/foot (푸시로드)</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Arm_A</t>
+          <t>Ankle2Feet / KneeB2AnkleB</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>54.76</v>
-      </c>
+        <v>167.54</v>
+      </c>
+      <c r="E32" s="9" t="n"/>
       <c r="F32" s="10">
         <f>IF(E32="","",E32/D32)</f>
         <v/>
       </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
-        </is>
-      </c>
+      <c r="G32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="92" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>shin/foot (푸시로드)</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / AnkleBraceA</t>
+          <t>Knee2Ankle / Knee2Ankle_IdleSide_1</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>40.54</v>
+        <v>130.43</v>
       </c>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="10">
@@ -3331,24 +2587,30 @@
     <row r="34" ht="92" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>shin/foot (푸시로드)</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / AnkleBraceB</t>
+          <t>Knee2Ankle / Knee2Ankle_RotorSide_2</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="E34" s="9" t="n"/>
+        <v>128.58</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>39.2</v>
+      </c>
       <c r="F34" s="10">
         <f>IF(E34="","",E34/D34)</f>
         <v/>
       </c>
-      <c r="G34" s="6" t="inlineStr"/>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>사진1 '39.2' · 보통 · 61.2 판 아래 X-래티스 판</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="92" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -3359,18 +2621,24 @@
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / KneeB2AnkleB</t>
+          <t>Knee2Ankle / Knee2Ankle_IdleSide_2</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>171.84</v>
-      </c>
-      <c r="E35" s="9" t="n"/>
+        <v>120.54</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>41.1</v>
+      </c>
       <c r="F35" s="10">
         <f>IF(E35="","",E35/D35)</f>
         <v/>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>사진5 '41.1 (91.1?)' · 불확실 · 대안: 91.1이면 Yaw2KneePlateB(297 g, 비율 0.31) · 반대편 X-래티스 판. 첫 글자가 4인지 9인지 불확실</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="92" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -3381,24 +2649,18 @@
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / KneeB2AnkleA</t>
+          <t>Ankle2Feet / Crank_A</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>168.52</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>56.9</v>
-      </c>
+        <v>94.02</v>
+      </c>
+      <c r="E36" s="9" t="n"/>
       <c r="F36" s="10">
         <f>IF(E36="","",E36/D36)</f>
         <v/>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>사진user '56.9 (사용자 확인)' · 확실 · 정강이 긴 트러스(motorb2ankle). 사진의 '36.9'는 3/5 오독 - 56.9 확정. A/B 짝 중 어느 쪽인지는 미확정</t>
-        </is>
-      </c>
+      <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="92" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -3409,24 +2671,18 @@
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_RotorSide_1</t>
+          <t>Ankle2Feet / Crank_B</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>161.35</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>61.2</v>
-      </c>
+        <v>92.43000000000001</v>
+      </c>
+      <c r="E37" s="9" t="n"/>
       <c r="F37" s="10">
         <f>IF(E37="","",E37/D37)</f>
         <v/>
       </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>사진1 '61.2' · 보통 · D형 판, 중앙 베어링 둘레 8볼트(로터 체결)</t>
-        </is>
-      </c>
+      <c r="G37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="92" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -3437,11 +2693,11 @@
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_IdleSide_1</t>
+          <t>Knee2Ankle / Knee2Ankle_Connector_A</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>130.53</v>
+        <v>44.62</v>
       </c>
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="10">
@@ -3459,24 +2715,18 @@
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_RotorSide_2</t>
+          <t>Knee2Ankle / Knee2Ankle_Connector_B</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>128.76</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>39.2</v>
-      </c>
+        <v>44.62</v>
+      </c>
+      <c r="E39" s="9" t="n"/>
       <c r="F39" s="10">
         <f>IF(E39="","",E39/D39)</f>
         <v/>
       </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>사진1 '39.2' · 보통 · 61.2 판 아래 X-래티스 판</t>
-        </is>
-      </c>
+      <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="92" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -3487,22 +2737,22 @@
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_IdleSide_2</t>
+          <t>Knee2Ankle / AnkleA2B_A_Support</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>123.63</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>41.1</v>
+        <v>40.82</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>12.7</v>
       </c>
       <c r="F40" s="10">
         <f>IF(E40="","",E40/D40)</f>
         <v/>
       </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>사진5 '41.1 (91.1?)' · 불확실 · 대안: 91.1이면 Yaw2KneePlateB(297 g, 비율 0.31) · 반대편 X-래티스 판. 첫 글자가 4인지 9인지 불확실</t>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>사진5 '12.7' · 보통 · 십자나사 4개 사각판, 비율 0.31 정확히 일치</t>
         </is>
       </c>
     </row>
@@ -3515,11 +2765,11 @@
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Crank_A</t>
+          <t>Knee2Ankle / AnkleA2B_A_Support (1)</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>73.89</v>
+        <v>40.82</v>
       </c>
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="10">
@@ -3537,18 +2787,24 @@
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Crank_B</t>
+          <t>Knee2Ankle / AnkleA2B_A_R (1)</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>72.17</v>
-      </c>
-      <c r="E42" s="9" t="n"/>
+        <v>32.27</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="F42" s="10">
         <f>IF(E42="","",E42/D42)</f>
         <v/>
       </c>
-      <c r="G42" s="6" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>사진7,8 '10.9' · 보통 · 대안: AnkleA2B_A_L (35 g, 0.31) - 같은 계열 4종(32~39 g) 중 어느 것인지는 미확정 · RS03 위쪽 마운트판, 두 사진에서 같은 값. 비율 0.34</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="92" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -3559,18 +2815,24 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_Connector_A</t>
+          <t>Knee2Ankle / AnkleA2B_A_L (1)</t>
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="E43" s="9" t="n"/>
+        <v>32.27</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>10.8</v>
+      </c>
       <c r="F43" s="10">
         <f>IF(E43="","",E43/D43)</f>
         <v/>
       </c>
-      <c r="G43" s="6" t="inlineStr"/>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>사진7 '10.8' · 불확실 · 대안: 같은 계열 4종 중 하나 · RS03 아래쪽 마운트판. 비율 0.34</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="92" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -3581,18 +2843,24 @@
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / Knee2Ankle_Connector_B</t>
+          <t>Knee2Ankle / AnkleA2B_A_L</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="E44" s="9" t="n"/>
+        <v>32.03</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>11.3</v>
+      </c>
       <c r="F44" s="10">
         <f>IF(E44="","",E44/D44)</f>
         <v/>
       </c>
-      <c r="G44" s="6" t="inlineStr"/>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>사진1 '11.3' · 불확실 · 대안: AnkleA2B_A_Support (1) (41 g) · RS03 아래 십자나사 2개 브래킷</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="92" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
@@ -3603,24 +2871,18 @@
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_Support</t>
+          <t>Ankle2Feet / Body19</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>40.82</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>12.7</v>
-      </c>
+        <v>31.88</v>
+      </c>
+      <c r="E45" s="9" t="n"/>
       <c r="F45" s="10">
         <f>IF(E45="","",E45/D45)</f>
         <v/>
       </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>사진5 '12.7' · 보통 · 십자나사 4개 사각판, 비율 0.31 정확히 일치</t>
-        </is>
-      </c>
+      <c r="G45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="92" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -3631,18 +2893,24 @@
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_Support (1)</t>
+          <t>Knee2Ankle / AnkleA2B_A_R</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>40.82</v>
-      </c>
-      <c r="E46" s="9" t="n"/>
+        <v>31.84</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="F46" s="10">
         <f>IF(E46="","",E46/D46)</f>
         <v/>
       </c>
-      <c r="G46" s="6" t="inlineStr"/>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>사진5 '12.0' · 불확실 · 대안: Crank_A_Cover (32 g) · 크랭크 옆 3볼트 브래킷</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="92" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -3653,1024 +2921,270 @@
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_R</t>
+          <t>Ankle2Feet / Body17</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>12</v>
-      </c>
+        <v>30.87</v>
+      </c>
+      <c r="E47" s="9" t="n"/>
       <c r="F47" s="10">
         <f>IF(E47="","",E47/D47)</f>
         <v/>
       </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>사진5 '12.0' · 불확실 · 대안: Crank_A_Cover (32 g) · 크랭크 옆 3볼트 브래킷</t>
-        </is>
-      </c>
+      <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="92" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Arm_B</t>
+          <t>HipYaw2Knee / Yaw2KneePlateA</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>38.77</v>
+        <v>321.95</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="F48" s="10">
         <f>IF(E48="","",E48/D48)</f>
         <v/>
       </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>알루미늄(출력 아님) · AB 푸시로드(긴 바) - 알루미늄 가공품, 출력 아님 (사용자 2026-08-23). CAD 질량 그대로</t>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>사진1,8 '98.1 (사진8은 98.4로도 읽힘)' · 보통 · 대안: Yaw2KneePlateB - 반대편 판 값 미확인 · 무릎 로터쪽 허벅지 트러스판. 두 사진 모두 이 판 - 같은 값의 판독 차이</t>
         </is>
       </c>
     </row>
     <row r="49" ht="92" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_L</t>
+          <t>HipYaw2Knee / HipYaw2Knee_Rotor</t>
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="E49" s="13" t="n">
-        <v>11.3</v>
-      </c>
+        <v>317.44</v>
+      </c>
+      <c r="E49" s="9" t="n"/>
       <c r="F49" s="10">
         <f>IF(E49="","",E49/D49)</f>
         <v/>
       </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>사진1 '11.3' · 불확실 · 대안: AnkleA2B_A_Support (1) (41 g) · RS03 아래 십자나사 2개 브래킷</t>
-        </is>
-      </c>
+      <c r="G49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="92" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_R (1)</t>
+          <t>HipYaw2Knee / Yaw2KneePlateB</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>10.9</v>
-      </c>
+        <v>296.74</v>
+      </c>
+      <c r="E50" s="9" t="n"/>
       <c r="F50" s="10">
         <f>IF(E50="","",E50/D50)</f>
         <v/>
       </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>사진7,8 '10.9' · 보통 · 대안: AnkleA2B_A_L (35 g, 0.31) - 같은 계열 4종(32~39 g) 중 어느 것인지는 미확정 · RS03 위쪽 마운트판, 두 사진에서 같은 값. 비율 0.34</t>
-        </is>
-      </c>
+      <c r="G50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="92" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Knee2Ankle / AnkleA2B_A_L (1)</t>
+          <t>HipYaw2Knee / HipYaw2Knee_outer</t>
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>10.8</v>
+        <v>189.43</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>63.3</v>
       </c>
       <c r="F51" s="10">
         <f>IF(E51="","",E51/D51)</f>
         <v/>
       </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>사진7 '10.8' · 불확실 · 대안: 같은 계열 4종 중 하나 · RS03 아래쪽 마운트판. 비율 0.34</t>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>사진user,8 '63.3 (사용자 확정: HipYaw2Knee_outer)' · 확실 · 요 모터 아래 바깥 링. 비율 0.45 = PLA 100 % 충전 상한(0.459) 바로 아래 - 이 부품은 꽉 채워 뽑은 것</t>
         </is>
       </c>
     </row>
     <row r="52" ht="92" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Crank_A_Cover</t>
+          <t>HipYaw2Knee / SupportA</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="E52" s="9" t="n"/>
+        <v>106.36</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>40</v>
+      </c>
       <c r="F52" s="10">
         <f>IF(E52="","",E52/D52)</f>
         <v/>
       </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>사진5 'R-A 라벨 아래 글자 판독 불가' · 미기입 · 둥근 3볼트 덮개판. 질량 미기입</t>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>사진2 ''4.0'' · 불확실 · 허벅지 육각 래티스 스트립. 4.0 g는 물리적으로 불가 - 40으로 해석. 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="53" ht="92" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Crank_B_Cover</t>
+          <t>HipYaw2Knee / SupportB</t>
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>30.92</v>
-      </c>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="10">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F53" s="15">
         <f>IF(E53="","",E53/D53)</f>
         <v/>
       </c>
-      <c r="G53" s="6" t="inlineStr"/>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>사진2 ''ㅣ0.5' (10.5? 40.5?)' · 불확실 · 반대편 스트립. 40.5면 비율 0.47로 PLA 상한 초과 → 판독 또는 배정 재확인</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="92" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Ankle2Feet / Ankle_Stopper_Pitch</t>
+          <t>CenterPin_RS03 / 4PI-12mm</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="E54" s="13" t="n">
-        <v>6</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="E54" s="9" t="n"/>
       <c r="F54" s="10">
         <f>IF(E54="","",E54/D54)</f>
         <v/>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>사진1,10 '6.0 (사진10은 6.9?)' · 불확실 · 발목 소형 부품. 비율 0.29~0.34</t>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>ø4 핀 — 출력 대상 아닐 수 있음</t>
         </is>
       </c>
     </row>
     <row r="55" ht="92" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>shoulder_pitch_link</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Shoulder-Pitch2Roll / Body3</t>
+          <t>CenterPin_RS03 / 4PI-12mm (2)</t>
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>107.17</v>
+        <v>0.4</v>
       </c>
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="10">
         <f>IF(E55="","",E55/D55)</f>
         <v/>
       </c>
-      <c r="G55" s="6" t="inlineStr"/>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>ø4 핀 — 출력 대상 아닐 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="92" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>shoulder_pitch_link</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Shoulder-Pitch2Roll / Body4</t>
+          <t>CenterPin_RS03 / 4PI-12mm (1)</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>107.17</v>
+        <v>0.4</v>
       </c>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="10">
         <f>IF(E56="","",E56/D56)</f>
         <v/>
       </c>
-      <c r="G56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="92" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>shoulder_pitch_link</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Shoulder-Pitch2Roll / Body2</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="n">
-        <v>83.26000000000001</v>
-      </c>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="10">
-        <f>IF(E57="","",E57/D57)</f>
-        <v/>
-      </c>
-      <c r="G57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58" ht="92" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / Yaw2KneePlateA</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>321.95</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="F58" s="10">
-        <f>IF(E58="","",E58/D58)</f>
-        <v/>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>사진1,8 '98.1 (사진8은 98.4로도 읽힘)' · 보통 · 대안: Yaw2KneePlateB - 반대편 판 값 미확인 · 무릎 로터쪽 허벅지 트러스판. 두 사진 모두 이 판 - 같은 값의 판독 차이</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="92" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / HipYaw2Knee_Rotor</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="n">
-        <v>317.19</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="F59" s="10">
-        <f>IF(E59="","",E59/D59)</f>
-        <v/>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>사진user,8 '63.3 (사용자: hipyaw2knee)' · 보통 · 대안: HipYaw2Knee_outer (140 g)면 0.45로 상한 직전 - 사용자 명칭 hipyaw2knee가 어느 바디인지 확인 · 요 로터에 붙는 두꺼운 원판(317 g). 사진8의 '6x.3'은 이 부품이었음. 비율 0.20 - 두꺼운 부품 저충전</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="92" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / Yaw2KneePlateB</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>296.74</v>
-      </c>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="10">
-        <f>IF(E60="","",E60/D60)</f>
-        <v/>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61" ht="92" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / HipYaw2Knee_outer</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>139.88</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F61" s="10">
-        <f>IF(E61="","",E61/D61)</f>
-        <v/>
-      </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>사진10 '44.9' · 보통 · 요 모터 바로 아래 흰 링. 비율 0.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="92" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / SupportA</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>106.36</v>
-      </c>
-      <c r="E62" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="F62" s="10">
-        <f>IF(E62="","",E62/D62)</f>
-        <v/>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>사진2 ''4.0'' · 불확실 · 허벅지 육각 래티스 스트립. 4.0 g는 물리적으로 불가 - 40으로 해석. 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="92" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>HipYaw2Knee / SupportB</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>87.06999999999999</v>
-      </c>
-      <c r="E63" s="13" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F63" s="15">
-        <f>IF(E63="","",E63/D63)</f>
-        <v/>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>사진2 ''ㅣ0.5' (10.5? 40.5?)' · 불확실 · 반대편 스트립. 40.5면 비율 0.47로 PLA 상한 초과 → 판독 또는 배정 재확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="92" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>CenterPin_RS03 / 4PI-12mm</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="10">
-        <f>IF(E64="","",E64/D64)</f>
-        <v/>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>ø4 핀 — 출력 대상 아닐 수 있음</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="92" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>CenterPin_RS03 / 4PI-12mm (2)</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="10">
-        <f>IF(E65="","",E65/D65)</f>
-        <v/>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>ø4 핀 — 출력 대상 아닐 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="92" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>CenterPin_RS03 / 4PI-12mm (1)</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E66" s="9" t="n"/>
-      <c r="F66" s="10">
-        <f>IF(E66="","",E66/D66)</f>
-        <v/>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>ø4 핀 — 출력 대상 아닐 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="92" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Waist2Torso / WaistYaw2based</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>311.61</v>
-      </c>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="10">
-        <f>IF(E67="","",E67/D67)</f>
-        <v/>
-      </c>
-      <c r="G67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68" ht="92" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>DR2020-375L</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>200.06</v>
-      </c>
-      <c r="E68" s="9" t="n"/>
-      <c r="F68" s="10">
-        <f>IF(E68="","",E68/D68)</f>
-        <v/>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="92" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>DR2020-375L (1)</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>200.06</v>
-      </c>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="10">
-        <f>IF(E69="","",E69/D69)</f>
-        <v/>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="92" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>DR2020-375L (3)</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>200.06</v>
-      </c>
-      <c r="E70" s="9" t="n"/>
-      <c r="F70" s="10">
-        <f>IF(E70="","",E70/D70)</f>
-        <v/>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="92" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>DR2020-375L (2)</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>200.06</v>
-      </c>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="10">
-        <f>IF(E71="","",E71/D71)</f>
-        <v/>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="92" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-160L_1</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>85.36</v>
-      </c>
-      <c r="E72" s="9" t="n"/>
-      <c r="F72" s="10">
-        <f>IF(E72="","",E72/D72)</f>
-        <v/>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="92" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-160L_2</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>85.36</v>
-      </c>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="10">
-        <f>IF(E73="","",E73/D73)</f>
-        <v/>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="92" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-160L_2 (1) / DF2020-160L_2</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="10">
-        <f>IF(E74="","",E74/D74)</f>
-        <v/>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="92" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-160L_1 (1) / DF2020-160L_1</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="10">
-        <f>IF(E75="","",E75/D75)</f>
-        <v/>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="92" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-85L_1</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="10">
-        <f>IF(E76="","",E76/D76)</f>
-        <v/>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="92" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-85L_2</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="10">
-        <f>IF(E77="","",E77/D77)</f>
-        <v/>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="92" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-85L_2 (1) / DF2020-85L_2</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="E78" s="9" t="n"/>
-      <c r="F78" s="10">
-        <f>IF(E78="","",E78/D78)</f>
-        <v/>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="92" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="n"/>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>DF2020-85L_3 / DF2020-85L_1</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="E79" s="9" t="n"/>
-      <c r="F79" s="10">
-        <f>IF(E79="","",E79/D79)</f>
-        <v/>
-      </c>
-      <c r="G79" s="11" t="inlineStr">
-        <is>
-          <t>2020 알루미늄 압출 프로파일 (구매품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="92" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body4</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="10">
-        <f>IF(E80="","",E80/D80)</f>
-        <v/>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-    </row>
-    <row r="81" ht="92" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="n"/>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body2</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="10">
-        <f>IF(E81="","",E81/D81)</f>
-        <v/>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-    </row>
-    <row r="82" ht="92" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body1</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="10">
-        <f>IF(E82="","",E82/D82)</f>
-        <v/>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-    </row>
-    <row r="83" ht="92" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body5</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="10">
-        <f>IF(E83="","",E83/D83)</f>
-        <v/>
-      </c>
-      <c r="G83" s="6" t="inlineStr"/>
-    </row>
-    <row r="84" ht="92" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body6</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="10">
-        <f>IF(E84="","",E84/D84)</f>
-        <v/>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-    </row>
-    <row r="85" ht="92" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>NeckYaw2Pitch / Body3</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="10">
-        <f>IF(E85="","",E85/D85)</f>
-        <v/>
-      </c>
-      <c r="G85" s="6" t="inlineStr"/>
-    </row>
-    <row r="86" ht="92" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Waist2Torso / WaistYaw-Assist</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="10">
-        <f>IF(E86="","",E86/D86)</f>
-        <v/>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="C87" s="16" t="inlineStr">
+    <row r="57">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="D87" s="17">
-        <f>SUM(D6:D86)</f>
-        <v/>
-      </c>
-      <c r="E87" s="17">
-        <f>SUM(E6:E86)</f>
+      <c r="D57" s="17">
+        <f>SUM(D6:D56)</f>
+        <v/>
+      </c>
+      <c r="E57" s="17">
+        <f>SUM(E6:E56)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G86"/>
+  <autoFilter ref="A5:G56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -4682,7 +3196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4733,19 +3247,19 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A4)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A4)</f>
         <v/>
       </c>
       <c r="C4" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A4,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D4" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A4,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E4" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A4,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A4,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -4756,272 +3270,203 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A5)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A5)</f>
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A5,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D5" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A5,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A5,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A5,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>arm_link (팔)</t>
+          <t>base_link (골반)</t>
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A6)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A6)</f>
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A6,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D6" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A6,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E6" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A6,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A6,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>base_link (골반)</t>
+          <t>foot_link (발)</t>
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A7)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A7)</f>
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A7,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A7,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A7,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A7,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>foot_link (발)</t>
+          <t>hip_pitch_link</t>
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A8)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A8)</f>
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A8,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A8,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A8,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A8,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>hip_pitch_link</t>
+          <t>hip_roll_link</t>
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A9)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A9)</f>
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A9,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A9,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A9,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A9,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>hip_roll_link</t>
+          <t>shin/foot (푸시로드)</t>
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A10)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A10)</f>
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A10,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A10,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A10,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A10,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>shin/foot (푸시로드)</t>
+          <t>shin_link (정강이)</t>
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A11)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A11)</f>
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A11,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D11" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A11,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E11" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A11,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A11,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>shin_link (정강이)</t>
+          <t>thigh_link (허벅지)</t>
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A12)</f>
+        <f>COUNTIF('알루미늄 부품'!$A$6:$A$56,A12)</f>
         <v/>
       </c>
       <c r="C12" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$D$6:$D$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A12,'알루미늄 부품'!$D$6:$D$56)</f>
         <v/>
       </c>
       <c r="D12" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86)</f>
+        <f>SUMIF('알루미늄 부품'!$A$6:$A$56,A12,'알루미늄 부품'!$E$6:$E$56)</f>
         <v/>
       </c>
       <c r="E12" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A12,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
+        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$56,A12,'알루미늄 부품'!$E$6:$E$56,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>shoulder_pitch_link</t>
-        </is>
-      </c>
-      <c r="B13" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$D$6:$D$86)</f>
-        <v/>
-      </c>
-      <c r="D13" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86)</f>
-        <v/>
-      </c>
-      <c r="E13" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A13,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>thigh_link (허벅지)</t>
-        </is>
-      </c>
-      <c r="B14" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$D$6:$D$86)</f>
-        <v/>
-      </c>
-      <c r="D14" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86)</f>
-        <v/>
-      </c>
-      <c r="E14" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A14,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>torso_link (몸통)</t>
-        </is>
-      </c>
-      <c r="B15" s="7">
-        <f>COUNTIF('알루미늄 부품'!$A$6:$A$86,A15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$D$6:$D$86)</f>
-        <v/>
-      </c>
-      <c r="D15" s="19">
-        <f>SUMIF('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86)</f>
-        <v/>
-      </c>
-      <c r="E15" s="19">
-        <f>COUNTIFS('알루미늄 부품'!$A$6:$A$86,A15,'알루미늄 부품'!$E$6:$E$86,"&lt;&gt;")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B16" s="20">
-        <f>SUM(B4:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
-        <f>SUM(C4:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>SUM(D4:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E4:E15)</f>
+      <c r="B13" s="20">
+        <f>SUM(B4:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="21">
+        <f>SUM(C4:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>SUM(D4:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>SUM(E4:E12)</f>
         <v/>
       </c>
     </row>
